--- a/data_extactor/batch_10_fa/trimmed/batch_0060_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0060_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | حقوق و مقررات دولتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارت‌پخش‌کن‌های بازی | کارکنان صندوق و باجه بازی | سرپرستان رده‌اول کارکنان خدمات بازی | ماموران نظارت و بازرسان بازی | متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | کارشناسان خدمات مشتریان</t>
+          <t>گردانندگان بازی‌های میزی و کازینویی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید دور | دید نزدیک | دقت در کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | چابکی انگشتان</t>
+          <t>بینایی دور | بینایی نزدیک | دقت کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های صدا و تصویر | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | تعمیرکاران و سرویس‌کاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تکنسین‌های نورپردازی | کارکنان و اپراتورهای چاپ و پردازش عکس | تکنسین‌های مهندسی صدا</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تکنسین‌های نورپردازی | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | متصدیان باجه و کرایه کالا | کارشناسان خدمات مشتریان | مهمانداران رستوران، سالن و کافی‌شاپ | متصدیان رختکن و اتاق پرو | متصدیان پذیرش و اطلاعات</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان رختکن، امانات و اتاق پرو | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>صندوق‌داران | متصدیان باجه و کرایه کالا | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | متصدیان پذیرش هتل و مراکز اقامتی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان حفاظتی تفریحی | متصدیان پارکینگ | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها</t>
+          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | متصدیان پارکینگ | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | طراحی | تولید و پردازش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی</t>
+          <t>هنرهای زیبا | طراحی | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | چابکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>الگوسازان پارچه و پوشاک | طراحان مد و لباس | کارکنان خشکشویی و لباسشویی | چهره‌پردازان و گریمورهای تئاتر و سینما | طراحان صحنه و دکور | دوزندگان دستی | خیاطان، دوزندگان لباس زنانه و دوزندگان سفارشی</t>
+          <t>الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | کارگران خشکشویی و رختشویخانه | چهره‌پردازان و گریموران تئاتر و سینما | طراحان صحنه و نمایشگاه | دوزندگان دستی | خیاطان و دوزندگان سفارشی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>باربرها و باربران هتل | متصدیان باجه و کرایه کالا | متصدیان سالن پذیرایی و کمک‌بارتندرها | متصدیان پذیرش هتل و مراکز اقامتی | کارکنان خشکشویی و لباسشویی | خدمتکاران و نظافتچیان خانه‌داری | فروشندگان خرده‌فروشی</t>
+          <t>متصدیان حمل بار و خدمات هتل | متصدیان باجه و کرایه کالا و خدمات | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | کارگران خشکشویی و رختشویخانه | خدمتکاران و نظافتچیان منازل و هتل‌ها | فروشندگان خرده‌فروشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | رایانه و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها | متصدیان و جامه داران لباس صحنه | متصدیان رختکن، امانات و اتاق پرو | مربیان و کارشناسان امور تفریحی و اوقات فراغت | راهنماهای تور و همراهان گردشگری | سایر کارکنان خدمات بازی و سرگرمی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن و بلیط‌گیرها | متصدیان و جامه داران لباس صحنه | متصدیان رختکن، امانات و اتاق پرو | کارکنان و متصدیان امور تفریحی و اوقات فراغت | راهنمایان تور و گردشگری | سایر کارکنان خدمات بازی و سرگرمی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | شیمی | روان‌شناسی | حقوق و مقررات دولتی | زیست‌شناسی | فلسفه و الهیات</t>
+          <t>خدمات مشتری و شخصی | شیمی | روان‌شناسی | قانون و دولت | زیست‌شناسی | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | پایداری دست و بازو | بیان شفاهی | استدلال قیاسی | چابکی دستی</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | بیان شفاهی | استدلال قیاسی | مهارت دستی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پزشکان قانونی | اپراتورهای کوره‌های جسدسوزی | متصدیان خدمات مراسم ترحیم | مدیران آرامستان‌ها و سالن‌های ترحیم | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | تکنسین‌های خون‌گیری (فلبوتومیست‌ها) | تکنسین‌های اتاق عمل</t>
+          <t>پزشکان قانونی و بازرسان مرگ مشکوک | اپراتورهای کوره‌های سوزاندن جسد | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران آرامستان‌ها و امور خدمات متوفیات | مدیران و برگزارکنندگان مراسم تشییع و تدفین | کارشناسان و تکنسین‌های خون‌گیری | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت آرامستان Mortware | سامانه HMIS Advantage | Microsoft Excel | Microsoft Word | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار مدیریت آرامستان Mortware | سامانه HMIS Advantage | Microsoft Excel | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی | حقوق و مقررات دولتی | شیمی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | قانون و دولت | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | پایداری دست و بازو | دقت در کنترل | قدرت ایستا | قدرت تنه | دید نزدیک | حساسیت به مسئله</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | قدرت ایستا | قدرت تنه | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | متصدیان خدمات مراسم ترحیم | مدیران آرامستان‌ها و سالن‌های ترحیم | کارگران جمع‌آوری و پاکسازی مواد خطرناک | تعمیرکاران ماشین‌آلات | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | کارگران بازیافت و تفکیک مواد</t>
+          <t>مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران آرامستان‌ها و امور خدمات متوفیات | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران تعمیر و نگهداری ماشین‌آلات | مدیران و برگزارکنندگان مراسم تشییع و تدفین | کارگران بازیافت و تفکیک پسماند</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری و دفتری | سامانه‌های مدیریت منابع انسانی iCIMS | Microsoft Excel | Microsoft Word | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار حسابداری | سامانه‌های مدیریت منابع انسانی iCIMS | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار iCIMS Talent Cloud</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باربرها و باربران هتل | اپراتورهای کوره‌های جسدسوزی | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | مدیران آرامستان‌ها و سالن‌های ترحیم | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | مراقبان خدمات شخصی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها</t>
+          <t>متصدیان حمل بار و خدمات هتل | اپراتورهای کوره‌های سوزاندن جسد | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | مدیران آرامستان‌ها و امور خدمات متوفیات | مدیران و برگزارکنندگان مراسم تشییع و تدفین | مراقبان خدمات شخصی و همراهان توان‌خواهان | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
